--- a/LLM_Extraction_and_CrossCritique/interactive-table/full_table/ITABLE_iotox.xlsx
+++ b/LLM_Extraction_and_CrossCritique/interactive-table/full_table/ITABLE_iotox.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhrub\Mayo-CoRAL\LLM_Extraction_and_CrossCritique\interactive-table\full_table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344BFA75-9FF2-4CB4-B5D6-68F90D524094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223FF059-2964-4FD3-A251-E4AB6AF8B282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3CDE4416-6C61-4C7D-9E97-69FC2F0D13D8}"/>
   </bookViews>
